--- a/doc/需求表表表xlsx.xlsx
+++ b/doc/需求表表表xlsx.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="10" documentId="11_62D72BBDDF23D8A1E41D5880F3C2DD66E906F2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8BC6A871-25E7-4546-81F6-4C139A696CB8}"/>
+  <xr:revisionPtr revIDLastSave="12" documentId="11_62D72BBDDF23D8A1E41D5880F3C2DD66E906F2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A71F52F-BFD6-42A1-AE3A-8DCDBE80F1A3}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -184,9 +184,6 @@
     <t>插在水中没有碰撞体积，可以有倾斜度，需要找好字体，内容栏里会显示字，埃及文怎么样？（还是中文吧）</t>
   </si>
   <si>
-    <t>所有敌人的碰撞体积都可以等美术效果出现后调整，目前全是圆形</t>
-  </si>
-  <si>
     <t>敌人-十字</t>
   </si>
   <si>
@@ -230,7 +227,12 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>毫无头绪。暂时不确定是否要加入boss所以不急。Boss的机制还在想。Boss具体是什么还是交给美术决定吧，或许提前定好boss是什么我也可以以此为基础想一想机制</t>
+    <t>所有敌人的碰撞体积都可以等美术效果出现后调整，目前全是圆形
+可能不需要了</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>毫无头绪。暂时不确定是否要加入boss所以不急。Boss的机制还在想。Boss具体是什么还是交给美术决定吧，或许提前定好boss是什么我也可以以此为基础想一想机制。Boss的美术需求在一张纸上</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -283,12 +285,15 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="2">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
       <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -518,6 +523,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -893,8 +902,8 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" t="s">
-        <v>23</v>
+      <c r="E8" s="2" t="s">
+        <v>36</v>
       </c>
     </row>
     <row r="9" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
@@ -902,13 +911,13 @@
         <v>7</v>
       </c>
       <c r="B9" t="s">
+        <v>23</v>
+      </c>
+      <c r="C9" t="s">
         <v>24</v>
       </c>
-      <c r="C9" t="s">
+      <c r="E9" t="s">
         <v>25</v>
-      </c>
-      <c r="E9" t="s">
-        <v>26</v>
       </c>
     </row>
     <row r="10" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
@@ -916,10 +925,10 @@
         <v>8</v>
       </c>
       <c r="B10" t="s">
+        <v>26</v>
+      </c>
+      <c r="C10" t="s">
         <v>27</v>
-      </c>
-      <c r="C10" t="s">
-        <v>28</v>
       </c>
     </row>
     <row r="11" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
@@ -927,10 +936,10 @@
         <v>9</v>
       </c>
       <c r="B11" t="s">
+        <v>28</v>
+      </c>
+      <c r="C11" t="s">
         <v>29</v>
-      </c>
-      <c r="C11" t="s">
-        <v>30</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.DISPIMG("ID_7401FDBCD63A4008BF0C582CBB9E3EF9",1)</f>
@@ -939,10 +948,10 @@
     </row>
     <row r="12" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
       <c r="A12" t="s">
+        <v>30</v>
+      </c>
+      <c r="B12" t="s">
         <v>31</v>
-      </c>
-      <c r="B12" t="s">
-        <v>32</v>
       </c>
     </row>
     <row r="13" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
@@ -950,13 +959,13 @@
         <v>10</v>
       </c>
       <c r="B13" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>33</v>
       </c>
-      <c r="C13" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>34</v>
-      </c>
-      <c r="E13" s="1" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="14" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
@@ -964,7 +973,7 @@
         <v>11</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="C14" s="1" t="s">
         <v>37</v>

--- a/doc/需求表表表xlsx.xlsx
+++ b/doc/需求表表表xlsx.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30131"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/e7b0b0416e4c7c0b/桌面/郭修齐/cgj2026/doc/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="12" documentId="11_62D72BBDDF23D8A1E41D5880F3C2DD66E906F2FA" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{4A71F52F-BFD6-42A1-AE3A-8DCDBE80F1A3}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="24240" windowHeight="13020" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="23145" windowHeight="8955"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -139,7 +133,7 @@
     <t>普通障碍</t>
   </si>
   <si>
-    <t>普通障碍是冥河上的一种障碍，灵魂和肉体都会被它挡住，静止的物体，比较适合做tilemap，预制摆放需要至少6种形状，具体形状需要和修齐沟通</t>
+    <t>普通障碍是冥河上的一种障碍，肉体会被它挡住，静止的物体，比较适合做tilemap，预制摆放需要至少6种形状，具体形状需要和修齐沟通</t>
   </si>
   <si>
     <t>括号内可选做，非括号为必要</t>
@@ -182,65 +176,65 @@
   </si>
   <si>
     <t>插在水中没有碰撞体积，可以有倾斜度，需要找好字体，内容栏里会显示字，埃及文怎么样？（还是中文吧）</t>
-  </si>
-  <si>
-    <t>敌人-十字</t>
-  </si>
-  <si>
-    <t>这个敌人设计的不太好，先当个占位符吧，我相信大家都希望有更贴近古埃及文化的敌人设计出现</t>
-  </si>
-  <si>
-    <t>esc打开设置查看按键映射</t>
-  </si>
-  <si>
-    <t>玩家</t>
-  </si>
-  <si>
-    <t>需要玩家悬浮的动画（一团火移动时没有风吹过的倾斜会奇怪，但先把主要元素实现最重要），连线的悬空小火球（只需要一个样式不需要拆分，需要可以被缩放，可以有动画，3帧就行很简单，每个火球岔开播放就会有随机的感觉，比不动要好）（灵魂打出卡牌的动画，突然火焰变猛烈？火焰炸裂开？），没张卡牌的反馈效果需要指导，会程序生成动画，现有动画已推到云端</t>
-  </si>
-  <si>
-    <t>检查点</t>
-  </si>
-  <si>
-    <t>冥河上的补给，与叙事的联系有待设计，现在是完全为玩法服务的，玩家可以在检查点获得一次卡牌奖励，两个玩家的检查点需要设置成对应玩家的颜色，一个检查点只能被特定一名玩家获取</t>
-  </si>
-  <si>
-    <t>最后</t>
-  </si>
-  <si>
-    <t>会出现的动态元素就这些了，UI，场景，卡牌样式，这些都不是我们的发挥空间，加油，全靠你们了美术大大</t>
-  </si>
-  <si>
-    <t>教学弹窗</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>在游戏开始时弹出的教学弹窗，两个玩家各一个，可能要做键盘版本和手柄版本，或是直接放一起。键盘：P1按Q出牌、按E换牌。P2按K出牌，按L换牌。手柄：按LB出牌，按RB换牌，两个玩家都一样</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>加油</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>boss</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>所有敌人的碰撞体积都可以等美术效果出现后调整，目前全是圆形
 可能不需要了</t>
-    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>敌人-十字</t>
+  </si>
+  <si>
+    <t>这个敌人设计的不太好，先当个占位符吧，我相信大家都希望有更贴近古埃及文化的敌人设计出现</t>
+  </si>
+  <si>
+    <t>esc打开设置查看按键映射</t>
+  </si>
+  <si>
+    <t>玩家</t>
+  </si>
+  <si>
+    <t>需要玩家悬浮的动画（一团火移动时没有风吹过的倾斜会奇怪，但先把主要元素实现最重要），连线的悬空小火球（只需要一个样式不需要拆分，需要可以被缩放，可以有动画，3帧就行很简单，每个火球岔开播放就会有随机的感觉，比不动要好）（灵魂打出卡牌的动画，突然火焰变猛烈？火焰炸裂开？），没张卡牌的反馈效果需要指导，会程序生成动画，现有动画已推到云端</t>
+  </si>
+  <si>
+    <t>检查点</t>
+  </si>
+  <si>
+    <t>冥河上的补给，与叙事的联系有待设计，现在是完全为玩法服务的，玩家可以在检查点获得一次卡牌奖励，两个玩家的检查点需要设置成对应玩家的颜色，一个检查点只能被特定一名玩家获取</t>
+  </si>
+  <si>
+    <t>最后</t>
+  </si>
+  <si>
+    <t>会出现的动态元素就这些了，UI，场景，卡牌样式，这些都不是我们的发挥空间，加油，全靠你们了美术大大</t>
+  </si>
+  <si>
+    <t>教学弹窗</t>
+  </si>
+  <si>
+    <t>在游戏开始时弹出的教学弹窗，两个玩家各一个，可能要做键盘版本和手柄版本，或是直接放一起。键盘：P1按Q出牌、按E换牌。P2按K出牌，按L换牌。手柄：按LB出牌，按RB换牌，两个玩家都一样</t>
+  </si>
+  <si>
+    <t>加油</t>
+  </si>
+  <si>
+    <t>boss</t>
   </si>
   <si>
     <t>毫无头绪。暂时不确定是否要加入boss所以不急。Boss的机制还在想。Boss具体是什么还是交给美术决定吧，或许提前定好boss是什么我也可以以此为基础想一想机制。Boss的美术需求在一张纸上</t>
-    <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="x14ac x16r2 xr xr9">
-  <fonts count="3" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr9="http://schemas.microsoft.com/office/spreadsheetml/2016/revision9" mc:Ignorable="xr9">
+  <numFmts count="4">
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="21">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -249,29 +243,352 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <sz val="9"/>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="宋体"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="宋体"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
       <color theme="1"/>
       <name val="宋体"/>
-      <family val="3"/>
-      <charset val="134"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="宋体"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -279,9 +596,251 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="4" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="4" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="5" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -289,165 +848,96 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="千位分隔" xfId="1" builtinId="3"/>
+    <cellStyle name="货币" xfId="2" builtinId="4"/>
+    <cellStyle name="百分比" xfId="3" builtinId="5"/>
+    <cellStyle name="千位分隔[0]" xfId="4" builtinId="6"/>
+    <cellStyle name="货币[0]" xfId="5" builtinId="7"/>
+    <cellStyle name="超链接" xfId="6" builtinId="8"/>
+    <cellStyle name="已访问的超链接" xfId="7" builtinId="9"/>
+    <cellStyle name="注释" xfId="8" builtinId="10"/>
+    <cellStyle name="警告文本" xfId="9" builtinId="11"/>
+    <cellStyle name="标题" xfId="10" builtinId="15"/>
+    <cellStyle name="解释性文本" xfId="11" builtinId="53"/>
+    <cellStyle name="标题 1" xfId="12" builtinId="16"/>
+    <cellStyle name="标题 2" xfId="13" builtinId="17"/>
+    <cellStyle name="标题 3" xfId="14" builtinId="18"/>
+    <cellStyle name="标题 4" xfId="15" builtinId="19"/>
+    <cellStyle name="输入" xfId="16" builtinId="20"/>
+    <cellStyle name="输出" xfId="17" builtinId="21"/>
+    <cellStyle name="计算" xfId="18" builtinId="22"/>
+    <cellStyle name="检查单元格" xfId="19" builtinId="23"/>
+    <cellStyle name="链接单元格" xfId="20" builtinId="24"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="好" xfId="22" builtinId="26"/>
+    <cellStyle name="差" xfId="23" builtinId="27"/>
+    <cellStyle name="适中" xfId="24" builtinId="28"/>
+    <cellStyle name="强调文字颜色 1" xfId="25" builtinId="29"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="26" builtinId="30"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="27" builtinId="31"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="28" builtinId="32"/>
+    <cellStyle name="强调文字颜色 2" xfId="29" builtinId="33"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="30" builtinId="34"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="31" builtinId="35"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="32" builtinId="36"/>
+    <cellStyle name="强调文字颜色 3" xfId="33" builtinId="37"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="34" builtinId="38"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="35" builtinId="39"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="强调文字颜色 4" xfId="37" builtinId="41"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="38" builtinId="42"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="39" builtinId="43"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="40" builtinId="44"/>
+    <cellStyle name="强调文字颜色 5" xfId="41" builtinId="45"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="42" builtinId="46"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="43" builtinId="47"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="44" builtinId="48"/>
+    <cellStyle name="强调文字颜色 6" xfId="45" builtinId="49"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="46" builtinId="50"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="47" builtinId="51"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="48" builtinId="52"/>
   </cellStyles>
   <dxfs count="17">
     <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-      </font>
+    </dxf>
+    <dxf>
       <fill>
         <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
         </patternFill>
       </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
     </dxf>
     <dxf>
       <font>
+        <b val="1"/>
         <color theme="1"/>
       </font>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
     </dxf>
     <dxf>
       <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <border>
-        <top style="thin">
-          <color theme="4"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <top style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </top>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-      <border>
-        <bottom style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
-        </bottom>
-      </border>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <fill>
-        <patternFill patternType="solid">
-          <fgColor theme="4" tint="0.79995117038483843"/>
-          <bgColor theme="4" tint="0.79995117038483843"/>
-        </patternFill>
-      </fill>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
-        <color theme="1"/>
-      </font>
-    </dxf>
-    <dxf>
-      <font>
-        <b/>
+        <b val="1"/>
         <color theme="1"/>
       </font>
       <border>
@@ -458,7 +948,7 @@
     </dxf>
     <dxf>
       <font>
-        <b/>
+        <b val="1"/>
         <color theme="0"/>
       </font>
       <fill>
@@ -486,47 +976,157 @@
           <color theme="4"/>
         </bottom>
         <horizontal style="thin">
-          <color theme="4" tint="0.39994506668294322"/>
+          <color theme="4" tint="0.399975585192419"/>
         </horizontal>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <color theme="1"/>
+      </font>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <border>
+        <top style="thin">
+          <color theme="4"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <top style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </top>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
+      </border>
+    </dxf>
+    <dxf>
+      <font>
+        <b val="1"/>
+        <color theme="1"/>
+      </font>
+      <fill>
+        <patternFill patternType="solid">
+          <fgColor theme="4" tint="0.799981688894314"/>
+          <bgColor theme="4" tint="0.799981688894314"/>
+        </patternFill>
+      </fill>
+      <border>
+        <bottom style="thin">
+          <color theme="4" tint="0.399975585192419"/>
+        </bottom>
       </border>
     </dxf>
   </dxfs>
   <tableStyles count="2" defaultTableStyle="TableStylePreset3_Accent1" defaultPivotStyle="PivotStylePreset2_Accent1">
     <tableStyle name="TableStylePreset3_Accent1" pivot="0" count="7" xr9:uid="{59DB682C-5494-4EDE-A608-00C9E5F0F923}">
-      <tableStyleElement type="wholeTable" dxfId="16"/>
-      <tableStyleElement type="headerRow" dxfId="15"/>
-      <tableStyleElement type="totalRow" dxfId="14"/>
-      <tableStyleElement type="firstColumn" dxfId="13"/>
-      <tableStyleElement type="lastColumn" dxfId="12"/>
-      <tableStyleElement type="firstRowStripe" dxfId="11"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="10"/>
+      <tableStyleElement type="wholeTable" dxfId="6"/>
+      <tableStyleElement type="headerRow" dxfId="5"/>
+      <tableStyleElement type="totalRow" dxfId="4"/>
+      <tableStyleElement type="firstColumn" dxfId="3"/>
+      <tableStyleElement type="lastColumn" dxfId="2"/>
+      <tableStyleElement type="firstRowStripe" dxfId="1"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="0"/>
     </tableStyle>
     <tableStyle name="PivotStylePreset2_Accent1" table="0" count="10" xr9:uid="{267968C8-6FFD-4C36-ACC1-9EA1FD1885CA}">
-      <tableStyleElement type="headerRow" dxfId="9"/>
-      <tableStyleElement type="totalRow" dxfId="8"/>
-      <tableStyleElement type="firstRowStripe" dxfId="7"/>
-      <tableStyleElement type="firstColumnStripe" dxfId="6"/>
-      <tableStyleElement type="firstSubtotalRow" dxfId="5"/>
-      <tableStyleElement type="secondSubtotalRow" dxfId="4"/>
-      <tableStyleElement type="firstRowSubheading" dxfId="3"/>
-      <tableStyleElement type="secondRowSubheading" dxfId="2"/>
-      <tableStyleElement type="pageFieldLabels" dxfId="1"/>
-      <tableStyleElement type="pageFieldValues" dxfId="0"/>
+      <tableStyleElement type="headerRow" dxfId="16"/>
+      <tableStyleElement type="totalRow" dxfId="15"/>
+      <tableStyleElement type="firstRowStripe" dxfId="14"/>
+      <tableStyleElement type="firstColumnStripe" dxfId="13"/>
+      <tableStyleElement type="firstSubtotalRow" dxfId="12"/>
+      <tableStyleElement type="secondSubtotalRow" dxfId="11"/>
+      <tableStyleElement type="firstRowSubheading" dxfId="10"/>
+      <tableStyleElement type="secondRowSubheading" dxfId="9"/>
+      <tableStyleElement type="pageFieldLabels" dxfId="8"/>
+      <tableStyleElement type="pageFieldValues" dxfId="7"/>
     </tableStyle>
   </tableStyles>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
     </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
-    </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -773,14 +1373,14 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:E14"/>
-  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15"/>
+  <sheetFormatPr defaultColWidth="9.25" defaultRowHeight="39.95" customHeight="1" outlineLevelCol="4"/>
   <cols>
     <col min="1" max="1" width="42.25" customWidth="1"/>
     <col min="2" max="2" width="22" customWidth="1"/>
@@ -789,7 +1389,7 @@
     <col min="5" max="5" width="27.25" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="1" customHeight="1" spans="1:5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -806,7 +1406,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="2" customHeight="1" spans="1:5">
       <c r="A2">
         <v>0</v>
       </c>
@@ -821,7 +1421,7 @@
         <v>=DISPIMG("ID_5DD507FB10D7438E829BD9067E5575A9",1)</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="3" customHeight="1" spans="1:5">
       <c r="A3">
         <v>1</v>
       </c>
@@ -839,7 +1439,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="4" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="4" customHeight="1" spans="1:5">
       <c r="A4">
         <v>2</v>
       </c>
@@ -853,7 +1453,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="5" customHeight="1" spans="1:5">
       <c r="A5">
         <v>3</v>
       </c>
@@ -864,7 +1464,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="6" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="6" customHeight="1" spans="1:5">
       <c r="A6">
         <v>4</v>
       </c>
@@ -878,7 +1478,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="7" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="7" customHeight="1" spans="1:5">
       <c r="A7">
         <v>5</v>
       </c>
@@ -892,7 +1492,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="8" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="8" customHeight="1" spans="1:5">
       <c r="A8">
         <v>6</v>
       </c>
@@ -902,85 +1502,85 @@
       <c r="C8" t="s">
         <v>22</v>
       </c>
-      <c r="E8" s="2" t="s">
-        <v>36</v>
+      <c r="E8" s="1" t="s">
+        <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="9" customHeight="1" spans="1:5">
       <c r="A9">
         <v>7</v>
       </c>
       <c r="B9" t="s">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="C9" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E9" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
     </row>
-    <row r="10" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="10" customHeight="1" spans="1:5">
       <c r="A10">
         <v>8</v>
       </c>
       <c r="B10" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="C10" t="s">
-        <v>27</v>
+        <v>28</v>
       </c>
     </row>
-    <row r="11" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="11" customHeight="1" spans="1:5">
       <c r="A11">
         <v>9</v>
       </c>
       <c r="B11" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="C11" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="D11" t="str">
         <f>_xlfn.DISPIMG("ID_7401FDBCD63A4008BF0C582CBB9E3EF9",1)</f>
         <v>=DISPIMG("ID_7401FDBCD63A4008BF0C582CBB9E3EF9",1)</v>
       </c>
     </row>
-    <row r="12" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="12" customHeight="1" spans="1:5">
       <c r="A12" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="B12" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
     </row>
-    <row r="13" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="13" customHeight="1" spans="1:5">
       <c r="A13">
         <v>10</v>
       </c>
-      <c r="B13" s="1" t="s">
-        <v>32</v>
-      </c>
-      <c r="C13" s="1" t="s">
+      <c r="B13" s="2" t="s">
         <v>33</v>
       </c>
-      <c r="E13" s="1" t="s">
+      <c r="C13" s="2" t="s">
         <v>34</v>
       </c>
+      <c r="E13" s="2" t="s">
+        <v>35</v>
+      </c>
     </row>
-    <row r="14" spans="1:5" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.15">
+    <row r="14" customHeight="1" spans="1:5">
       <c r="A14">
         <v>11</v>
       </c>
-      <c r="B14" s="1" t="s">
-        <v>35</v>
-      </c>
-      <c r="C14" s="1" t="s">
+      <c r="B14" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>37</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="1" type="noConversion"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <headerFooter/>
 </worksheet>
 </file>